--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -794,12 +794,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454773.6473974845</v>
+        <v>454774</v>
       </c>
       <c r="R3" t="n">
-        <v>6463175.151379989</v>
+        <v>6463175</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +859,9 @@
           <t>1989-05-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-05-30</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>96925</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454773.6473974845</v>
+        <v>454774</v>
       </c>
       <c r="R2" t="n">
-        <v>6463175.151379989</v>
+        <v>6463175</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1989-05-30</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-05-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99198</v>
+        <v>99206</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98608</v>
+        <v>98616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99206</v>
+        <v>99212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98616</v>
+        <v>98622</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99212</v>
+        <v>99215</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99215</v>
+        <v>99220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99220</v>
+        <v>99221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99221</v>
+        <v>99248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99248</v>
+        <v>99261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99261</v>
+        <v>99265</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 13199-2021 artfynd.xlsx
+++ b/artfynd/A 13199-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>4696313</v>
       </c>
       <c r="B2" t="n">
-        <v>99265</v>
+        <v>99272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>2932914</v>
       </c>
       <c r="B3" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
